--- a/DANE/Katalog.xlsx
+++ b/DANE/Katalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maciej Kozłowski\Documents\Code\AutobusMZA\DANE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0424B421-7266-45DA-A27E-F43C188D18E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C644C78B-B2FA-458D-B2E8-A1BED263CC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="1930" windowWidth="14400" windowHeight="8170" xr2:uid="{5CDE761A-FA52-48B0-BB0D-A12883B0D50B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5CDE761A-FA52-48B0-BB0D-A12883B0D50B}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>KATALOG</t>
   </si>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>RaceBox_25_04_161</t>
-  </si>
-  <si>
-    <t>stoptimes_161_OLE_ZBG</t>
-  </si>
-  <si>
-    <t>stoptimes_161_ZBG_OLE</t>
   </si>
   <si>
     <t>27-04-229</t>
@@ -519,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025426F0-80D7-4A8D-9A13-79533947D7A8}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.6328125" customWidth="1"/>
@@ -535,34 +529,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
         <v>26</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -697,64 +691,41 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>1004</v>
+        <v>1421</v>
       </c>
       <c r="K7">
-        <v>161</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>1421</v>
+        <v>1004</v>
       </c>
       <c r="K8">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9">
-        <v>1004</v>
-      </c>
-      <c r="K9">
         <v>161</v>
       </c>
     </row>
